--- a/assets/excel/2026_5-1-2.xlsx
+++ b/assets/excel/2026_5-1-2.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Hannover\Dez15_Uebergreifende_Analysen\Projekte\Integrationsmonitoring\Schlesier\MT_Site\assets\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DF9B649-2977-4A39-84CD-682E6AF21D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDDAC2CE-14AE-452E-A80B-3956D7DA8F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{4424B46B-A95E-48DA-B113-8E8F86BF46C8}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{4424B46B-A95E-48DA-B113-8E8F86BF46C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -409,10 +406,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -420,46 +413,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -471,14 +428,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
@@ -490,6 +441,52 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -508,978 +505,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="5-1-2_Download"/>
-      <sheetName val="2021"/>
-      <sheetName val="2022"/>
-      <sheetName val="2023"/>
-      <sheetName val="2024"/>
-      <sheetName val="2025"/>
-      <sheetName val="5-1-2_CSV_Vorbereitung"/>
-      <sheetName val="5-1-2_CSV_Export"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="12">
-          <cell r="C12">
-            <v>1838.92</v>
-          </cell>
-          <cell r="E12">
-            <v>2089.69</v>
-          </cell>
-          <cell r="G12">
-            <v>3928.61</v>
-          </cell>
-          <cell r="I12">
-            <v>370.59</v>
-          </cell>
-          <cell r="K12">
-            <v>495.85</v>
-          </cell>
-          <cell r="M12">
-            <v>866.43</v>
-          </cell>
-          <cell r="O12">
-            <v>272.37</v>
-          </cell>
-          <cell r="Q12">
-            <v>374.64</v>
-          </cell>
-          <cell r="S12">
-            <v>647.01</v>
-          </cell>
-          <cell r="U12">
-            <v>98.22</v>
-          </cell>
-          <cell r="W12">
-            <v>121.21</v>
-          </cell>
-          <cell r="Y12">
-            <v>219.43</v>
-          </cell>
-          <cell r="AA12">
-            <v>1468.33</v>
-          </cell>
-          <cell r="AC12">
-            <v>1593.85</v>
-          </cell>
-          <cell r="AE12">
-            <v>3062.18</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="C13">
-            <v>1785.3</v>
-          </cell>
-          <cell r="E13">
-            <v>2009.82</v>
-          </cell>
-          <cell r="F13">
-            <v>3901.64</v>
-          </cell>
-          <cell r="I13">
-            <v>352.14</v>
-          </cell>
-          <cell r="K13">
-            <v>463.59</v>
-          </cell>
-          <cell r="M13">
-            <v>815.73</v>
-          </cell>
-          <cell r="O13">
-            <v>258.10000000000002</v>
-          </cell>
-          <cell r="Q13">
-            <v>350.04</v>
-          </cell>
-          <cell r="S13">
-            <v>608.14</v>
-          </cell>
-          <cell r="U13">
-            <v>94.04</v>
-          </cell>
-          <cell r="W13">
-            <v>113.54</v>
-          </cell>
-          <cell r="Y13">
-            <v>207.59</v>
-          </cell>
-          <cell r="AA13">
-            <v>1433.16</v>
-          </cell>
-          <cell r="AC13">
-            <v>1546.23</v>
-          </cell>
-          <cell r="AE13">
-            <v>2979.39</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="C14">
-            <v>53.62</v>
-          </cell>
-          <cell r="E14">
-            <v>79.87</v>
-          </cell>
-          <cell r="G14">
-            <v>133.49</v>
-          </cell>
-          <cell r="I14">
-            <v>18.440000000000001</v>
-          </cell>
-          <cell r="K14">
-            <v>32.26</v>
-          </cell>
-          <cell r="M14">
-            <v>50.7</v>
-          </cell>
-          <cell r="O14">
-            <v>14.27</v>
-          </cell>
-          <cell r="Q14">
-            <v>24.59</v>
-          </cell>
-          <cell r="S14">
-            <v>38.86</v>
-          </cell>
-          <cell r="U14">
-            <v>4.17</v>
-          </cell>
-          <cell r="W14">
-            <v>7.67</v>
-          </cell>
-          <cell r="Y14">
-            <v>11.84</v>
-          </cell>
-          <cell r="AA14">
-            <v>35.18</v>
-          </cell>
-          <cell r="AC14">
-            <v>47.61</v>
-          </cell>
-          <cell r="AE14">
-            <v>82.79</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="C15">
-            <v>2523.0100000000002</v>
-          </cell>
-          <cell r="E15">
-            <v>2573.46</v>
-          </cell>
-          <cell r="G15">
-            <v>5096.47</v>
-          </cell>
-          <cell r="I15">
-            <v>595.53</v>
-          </cell>
-          <cell r="K15">
-            <v>645.01</v>
-          </cell>
-          <cell r="M15">
-            <v>1240.54</v>
-          </cell>
-          <cell r="O15">
-            <v>438.06</v>
-          </cell>
-          <cell r="Q15">
-            <v>469.43</v>
-          </cell>
-          <cell r="S15">
-            <v>907.49</v>
-          </cell>
-          <cell r="U15">
-            <v>157.47</v>
-          </cell>
-          <cell r="W15">
-            <v>175.58</v>
-          </cell>
-          <cell r="Y15">
-            <v>333.05</v>
-          </cell>
-          <cell r="AA15">
-            <v>1927.48</v>
-          </cell>
-          <cell r="AC15">
-            <v>1928.45</v>
-          </cell>
-          <cell r="AE15">
-            <v>3855.93</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2">
-        <row r="12">
-          <cell r="C12">
-            <v>1897.1</v>
-          </cell>
-          <cell r="E12">
-            <v>2129.81</v>
-          </cell>
-          <cell r="G12">
-            <v>4026.91</v>
-          </cell>
-          <cell r="I12">
-            <v>405.71</v>
-          </cell>
-          <cell r="K12">
-            <v>524.71</v>
-          </cell>
-          <cell r="M12">
-            <v>930.42</v>
-          </cell>
-          <cell r="O12">
-            <v>303.7</v>
-          </cell>
-          <cell r="Q12">
-            <v>405.86</v>
-          </cell>
-          <cell r="S12">
-            <v>709.56</v>
-          </cell>
-          <cell r="U12">
-            <v>102</v>
-          </cell>
-          <cell r="W12">
-            <v>118.86</v>
-          </cell>
-          <cell r="Y12">
-            <v>220.86</v>
-          </cell>
-          <cell r="AA12">
-            <v>1491.39</v>
-          </cell>
-          <cell r="AC12">
-            <v>1605.1</v>
-          </cell>
-          <cell r="AE12">
-            <v>3096.49</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="C13">
-            <v>1849.36</v>
-          </cell>
-          <cell r="E13">
-            <v>2060.35</v>
-          </cell>
-          <cell r="F13">
-            <v>4036.67</v>
-          </cell>
-          <cell r="I13">
-            <v>388.71</v>
-          </cell>
-          <cell r="K13">
-            <v>496.53</v>
-          </cell>
-          <cell r="M13">
-            <v>885.24</v>
-          </cell>
-          <cell r="O13">
-            <v>290.11</v>
-          </cell>
-          <cell r="Q13">
-            <v>382.69</v>
-          </cell>
-          <cell r="S13">
-            <v>672.8</v>
-          </cell>
-          <cell r="U13">
-            <v>98.59</v>
-          </cell>
-          <cell r="W13">
-            <v>113.84</v>
-          </cell>
-          <cell r="Y13">
-            <v>212.44</v>
-          </cell>
-          <cell r="AA13">
-            <v>1460.65</v>
-          </cell>
-          <cell r="AC13">
-            <v>1563.81</v>
-          </cell>
-          <cell r="AE13">
-            <v>3024.47</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="C14">
-            <v>47.74</v>
-          </cell>
-          <cell r="E14">
-            <v>69.459999999999994</v>
-          </cell>
-          <cell r="G14">
-            <v>117.2</v>
-          </cell>
-          <cell r="I14">
-            <v>17</v>
-          </cell>
-          <cell r="K14">
-            <v>28.18</v>
-          </cell>
-          <cell r="M14">
-            <v>45.18</v>
-          </cell>
-          <cell r="O14">
-            <v>13.59</v>
-          </cell>
-          <cell r="Q14">
-            <v>23.17</v>
-          </cell>
-          <cell r="S14">
-            <v>36.76</v>
-          </cell>
-          <cell r="U14">
-            <v>3.41</v>
-          </cell>
-          <cell r="W14">
-            <v>5.01</v>
-          </cell>
-          <cell r="Y14">
-            <v>8.42</v>
-          </cell>
-          <cell r="AA14">
-            <v>30.74</v>
-          </cell>
-          <cell r="AC14">
-            <v>41.28</v>
-          </cell>
-          <cell r="AE14">
-            <v>72.02</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="C15">
-            <v>2545.71</v>
-          </cell>
-          <cell r="E15">
-            <v>2583.71</v>
-          </cell>
-          <cell r="G15">
-            <v>5129.41</v>
-          </cell>
-          <cell r="I15">
-            <v>633.20000000000005</v>
-          </cell>
-          <cell r="K15">
-            <v>667.3</v>
-          </cell>
-          <cell r="M15">
-            <v>1300.5</v>
-          </cell>
-          <cell r="O15">
-            <v>475.71</v>
-          </cell>
-          <cell r="Q15">
-            <v>495.43</v>
-          </cell>
-          <cell r="S15">
-            <v>971.14</v>
-          </cell>
-          <cell r="U15">
-            <v>157.49</v>
-          </cell>
-          <cell r="W15">
-            <v>171.86</v>
-          </cell>
-          <cell r="Y15">
-            <v>329.36</v>
-          </cell>
-          <cell r="AA15">
-            <v>1912.51</v>
-          </cell>
-          <cell r="AC15">
-            <v>1916.41</v>
-          </cell>
-          <cell r="AE15">
-            <v>3828.92</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3">
-        <row r="12">
-          <cell r="C12">
-            <v>1906.18</v>
-          </cell>
-          <cell r="E12">
-            <v>2138.19</v>
-          </cell>
-          <cell r="G12">
-            <v>4044.37</v>
-          </cell>
-          <cell r="I12">
-            <v>415.22</v>
-          </cell>
-          <cell r="K12">
-            <v>538.70000000000005</v>
-          </cell>
-          <cell r="M12">
-            <v>953.93</v>
-          </cell>
-          <cell r="O12">
-            <v>309.17</v>
-          </cell>
-          <cell r="Q12">
-            <v>412.89</v>
-          </cell>
-          <cell r="S12">
-            <v>722.05</v>
-          </cell>
-          <cell r="U12">
-            <v>106.06</v>
-          </cell>
-          <cell r="W12">
-            <v>125.81</v>
-          </cell>
-          <cell r="Y12">
-            <v>231.87</v>
-          </cell>
-          <cell r="AA12">
-            <v>1490.96</v>
-          </cell>
-          <cell r="AC12">
-            <v>1599.49</v>
-          </cell>
-          <cell r="AE12">
-            <v>3090.45</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="C13">
-            <v>1857.82</v>
-          </cell>
-          <cell r="E13">
-            <v>2071.71</v>
-          </cell>
-          <cell r="F13">
-            <v>4066.89</v>
-          </cell>
-          <cell r="I13">
-            <v>396.2</v>
-          </cell>
-          <cell r="K13">
-            <v>510.39</v>
-          </cell>
-          <cell r="M13">
-            <v>906.59</v>
-          </cell>
-          <cell r="O13">
-            <v>293.74</v>
-          </cell>
-          <cell r="Q13">
-            <v>391.65</v>
-          </cell>
-          <cell r="S13">
-            <v>685.39</v>
-          </cell>
-          <cell r="U13">
-            <v>102.46</v>
-          </cell>
-          <cell r="W13">
-            <v>118.74</v>
-          </cell>
-          <cell r="Y13">
-            <v>221.2</v>
-          </cell>
-          <cell r="AA13">
-            <v>1461.62</v>
-          </cell>
-          <cell r="AC13">
-            <v>1561.32</v>
-          </cell>
-          <cell r="AE13">
-            <v>3022.94</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="C14">
-            <v>48.36</v>
-          </cell>
-          <cell r="E14">
-            <v>66.48</v>
-          </cell>
-          <cell r="G14">
-            <v>114.84</v>
-          </cell>
-          <cell r="I14">
-            <v>19.02</v>
-          </cell>
-          <cell r="K14">
-            <v>28.31</v>
-          </cell>
-          <cell r="M14">
-            <v>47.34</v>
-          </cell>
-          <cell r="O14">
-            <v>15.43</v>
-          </cell>
-          <cell r="Q14">
-            <v>21.24</v>
-          </cell>
-          <cell r="S14">
-            <v>36.67</v>
-          </cell>
-          <cell r="U14">
-            <v>3.6</v>
-          </cell>
-          <cell r="W14">
-            <v>7.07</v>
-          </cell>
-          <cell r="Y14">
-            <v>10.67</v>
-          </cell>
-          <cell r="AA14">
-            <v>29.34</v>
-          </cell>
-          <cell r="AC14">
-            <v>38.17</v>
-          </cell>
-          <cell r="AE14">
-            <v>67.5</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="C15">
-            <v>2556.8000000000002</v>
-          </cell>
-          <cell r="E15">
-            <v>2591.2600000000002</v>
-          </cell>
-          <cell r="G15">
-            <v>5148.07</v>
-          </cell>
-          <cell r="I15">
-            <v>659.63</v>
-          </cell>
-          <cell r="K15">
-            <v>689.45</v>
-          </cell>
-          <cell r="M15">
-            <v>1349.07</v>
-          </cell>
-          <cell r="O15">
-            <v>498.48</v>
-          </cell>
-          <cell r="Q15">
-            <v>515.29</v>
-          </cell>
-          <cell r="S15">
-            <v>1013.77</v>
-          </cell>
-          <cell r="U15">
-            <v>161.15</v>
-          </cell>
-          <cell r="W15">
-            <v>174.15</v>
-          </cell>
-          <cell r="Y15">
-            <v>335.3</v>
-          </cell>
-          <cell r="AA15">
-            <v>1897.18</v>
-          </cell>
-          <cell r="AC15">
-            <v>1901.82</v>
-          </cell>
-          <cell r="AE15">
-            <v>3799</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="4">
-        <row r="12">
-          <cell r="C12">
-            <v>1910.81</v>
-          </cell>
-          <cell r="E12">
-            <v>2138.31</v>
-          </cell>
-          <cell r="G12">
-            <v>4049.12</v>
-          </cell>
-          <cell r="I12">
-            <v>461.74</v>
-          </cell>
-          <cell r="K12">
-            <v>574.83000000000004</v>
-          </cell>
-          <cell r="M12">
-            <v>1036.58</v>
-          </cell>
-          <cell r="O12">
-            <v>330.65</v>
-          </cell>
-          <cell r="Q12">
-            <v>428.48</v>
-          </cell>
-          <cell r="S12">
-            <v>759.14</v>
-          </cell>
-          <cell r="U12">
-            <v>131.09</v>
-          </cell>
-          <cell r="W12">
-            <v>146.35</v>
-          </cell>
-          <cell r="Y12">
-            <v>277.44</v>
-          </cell>
-          <cell r="AA12">
-            <v>1449.06</v>
-          </cell>
-          <cell r="AC12">
-            <v>1563.48</v>
-          </cell>
-          <cell r="AE12">
-            <v>3012.54</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="C13">
-            <v>1852.1</v>
-          </cell>
-          <cell r="E13">
-            <v>2068.16</v>
-          </cell>
-          <cell r="F13">
-            <v>4065.13</v>
-          </cell>
-          <cell r="I13">
-            <v>433.07</v>
-          </cell>
-          <cell r="K13">
-            <v>542.54999999999995</v>
-          </cell>
-          <cell r="M13">
-            <v>975.62</v>
-          </cell>
-          <cell r="O13">
-            <v>309.29000000000002</v>
-          </cell>
-          <cell r="Q13">
-            <v>405.16</v>
-          </cell>
-          <cell r="S13">
-            <v>714.45</v>
-          </cell>
-          <cell r="U13">
-            <v>123.78</v>
-          </cell>
-          <cell r="W13">
-            <v>137.4</v>
-          </cell>
-          <cell r="Y13">
-            <v>261.17</v>
-          </cell>
-          <cell r="AA13">
-            <v>1419.03</v>
-          </cell>
-          <cell r="AC13">
-            <v>1525.61</v>
-          </cell>
-          <cell r="AE13">
-            <v>2944.64</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="C14">
-            <v>58.71</v>
-          </cell>
-          <cell r="E14">
-            <v>70.150000000000006</v>
-          </cell>
-          <cell r="G14">
-            <v>128.86000000000001</v>
-          </cell>
-          <cell r="I14">
-            <v>28.68</v>
-          </cell>
-          <cell r="K14">
-            <v>32.28</v>
-          </cell>
-          <cell r="M14">
-            <v>60.96</v>
-          </cell>
-          <cell r="O14">
-            <v>21.36</v>
-          </cell>
-          <cell r="Q14">
-            <v>23.32</v>
-          </cell>
-          <cell r="S14">
-            <v>44.69</v>
-          </cell>
-          <cell r="U14">
-            <v>7.31</v>
-          </cell>
-          <cell r="W14">
-            <v>8.9600000000000009</v>
-          </cell>
-          <cell r="Y14">
-            <v>16.27</v>
-          </cell>
-          <cell r="AA14">
-            <v>30.03</v>
-          </cell>
-          <cell r="AC14">
-            <v>37.869999999999997</v>
-          </cell>
-          <cell r="AE14">
-            <v>67.900000000000006</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="C15">
-            <v>2547.89</v>
-          </cell>
-          <cell r="E15">
-            <v>2595.0100000000002</v>
-          </cell>
-          <cell r="G15">
-            <v>5142.8999999999996</v>
-          </cell>
-          <cell r="I15">
-            <v>712.41</v>
-          </cell>
-          <cell r="K15">
-            <v>735.94</v>
-          </cell>
-          <cell r="M15">
-            <v>1448.35</v>
-          </cell>
-          <cell r="O15">
-            <v>524.35</v>
-          </cell>
-          <cell r="Q15">
-            <v>539.30999999999995</v>
-          </cell>
-          <cell r="S15">
-            <v>1063.6600000000001</v>
-          </cell>
-          <cell r="U15">
-            <v>188.06</v>
-          </cell>
-          <cell r="W15">
-            <v>196.63</v>
-          </cell>
-          <cell r="Y15">
-            <v>384.69</v>
-          </cell>
-          <cell r="AA15">
-            <v>1835.48</v>
-          </cell>
-          <cell r="AC15">
-            <v>1859.07</v>
-          </cell>
-          <cell r="AE15">
-            <v>3694.55</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="5">
-        <row r="12">
-          <cell r="C12">
-            <v>1914.11</v>
-          </cell>
-          <cell r="E12">
-            <v>2144.12</v>
-          </cell>
-          <cell r="G12">
-            <v>4058.23</v>
-          </cell>
-          <cell r="I12">
-            <v>474.36</v>
-          </cell>
-          <cell r="K12">
-            <v>595.69000000000005</v>
-          </cell>
-          <cell r="M12">
-            <v>1070.06</v>
-          </cell>
-          <cell r="O12">
-            <v>341.23</v>
-          </cell>
-          <cell r="Q12">
-            <v>444.2</v>
-          </cell>
-          <cell r="S12">
-            <v>785.44</v>
-          </cell>
-          <cell r="U12">
-            <v>133.13</v>
-          </cell>
-          <cell r="W12">
-            <v>151.49</v>
-          </cell>
-          <cell r="Y12">
-            <v>284.62</v>
-          </cell>
-          <cell r="AA12">
-            <v>1439.75</v>
-          </cell>
-          <cell r="AC12">
-            <v>1548.43</v>
-          </cell>
-          <cell r="AE12">
-            <v>2988.17</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="C13">
-            <v>1854.45</v>
-          </cell>
-          <cell r="E13">
-            <v>2060.5300000000002</v>
-          </cell>
-          <cell r="F13">
-            <v>4063.22</v>
-          </cell>
-          <cell r="I13">
-            <v>445.71</v>
-          </cell>
-          <cell r="K13">
-            <v>553.67999999999995</v>
-          </cell>
-          <cell r="M13">
-            <v>999.38</v>
-          </cell>
-          <cell r="O13">
-            <v>320.10000000000002</v>
-          </cell>
-          <cell r="Q13">
-            <v>411.75</v>
-          </cell>
-          <cell r="S13">
-            <v>731.85</v>
-          </cell>
-          <cell r="U13">
-            <v>125.6</v>
-          </cell>
-          <cell r="W13">
-            <v>141.93</v>
-          </cell>
-          <cell r="Y13">
-            <v>267.52999999999997</v>
-          </cell>
-          <cell r="AA13">
-            <v>1408.75</v>
-          </cell>
-          <cell r="AC13">
-            <v>1506.85</v>
-          </cell>
-          <cell r="AE13">
-            <v>2915.6</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="C14">
-            <v>59.66</v>
-          </cell>
-          <cell r="E14">
-            <v>83.59</v>
-          </cell>
-          <cell r="G14">
-            <v>143.25</v>
-          </cell>
-          <cell r="I14">
-            <v>28.66</v>
-          </cell>
-          <cell r="K14">
-            <v>42.02</v>
-          </cell>
-          <cell r="M14">
-            <v>70.67</v>
-          </cell>
-          <cell r="O14">
-            <v>21.13</v>
-          </cell>
-          <cell r="Q14">
-            <v>32.450000000000003</v>
-          </cell>
-          <cell r="S14">
-            <v>53.58</v>
-          </cell>
-          <cell r="U14">
-            <v>7.53</v>
-          </cell>
-          <cell r="W14">
-            <v>9.56</v>
-          </cell>
-          <cell r="Y14">
-            <v>17.09</v>
-          </cell>
-          <cell r="AA14">
-            <v>31</v>
-          </cell>
-          <cell r="AC14">
-            <v>41.57</v>
-          </cell>
-          <cell r="AE14">
-            <v>72.569999999999993</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="C15">
-            <v>2537.71</v>
-          </cell>
-          <cell r="E15">
-            <v>2583.0300000000002</v>
-          </cell>
-          <cell r="G15">
-            <v>5120.74</v>
-          </cell>
-          <cell r="I15">
-            <v>718.9</v>
-          </cell>
-          <cell r="K15">
-            <v>754.35</v>
-          </cell>
-          <cell r="M15">
-            <v>1473.25</v>
-          </cell>
-          <cell r="O15">
-            <v>523.89</v>
-          </cell>
-          <cell r="Q15">
-            <v>550.96</v>
-          </cell>
-          <cell r="S15">
-            <v>1074.8499999999999</v>
-          </cell>
-          <cell r="U15">
-            <v>195.01</v>
-          </cell>
-          <cell r="W15">
-            <v>203.4</v>
-          </cell>
-          <cell r="Y15">
-            <v>398.4</v>
-          </cell>
-          <cell r="AA15">
-            <v>1818.81</v>
-          </cell>
-          <cell r="AC15">
-            <v>1828.68</v>
-          </cell>
-          <cell r="AE15">
-            <v>3647.49</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1803,234 +828,234 @@
     </row>
     <row r="2" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="M3" s="9"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="M3" s="8"/>
     </row>
     <row r="4" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="M4" s="9"/>
+      <c r="M4" s="8"/>
     </row>
     <row r="5" spans="2:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="10"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
     </row>
     <row r="6" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14" t="s">
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14" t="s">
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="O6" s="14"/>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="14"/>
-      <c r="R6" s="15"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="25"/>
     </row>
     <row r="7" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="16"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="13" t="s">
+      <c r="B7" s="31"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13" t="s">
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="J7" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13" t="s">
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="O7" s="13" t="s">
+      <c r="O7" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="18"/>
+      <c r="P7" s="26"/>
+      <c r="Q7" s="26"/>
+      <c r="R7" s="35"/>
     </row>
     <row r="8" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="16"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="19" t="s">
+      <c r="B8" s="31"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="14"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="19" t="s">
+      <c r="H8" s="24"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="K8" s="20" t="s">
+      <c r="K8" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="14" t="s">
+      <c r="L8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="M8" s="14"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="19" t="s">
+      <c r="M8" s="24"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="P8" s="20" t="s">
+      <c r="P8" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="Q8" s="14" t="s">
+      <c r="Q8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="R8" s="15"/>
+      <c r="R8" s="25"/>
     </row>
     <row r="9" spans="2:19" s="5" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="16"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="23" t="s">
+      <c r="B9" s="31"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="H9" s="23" t="s">
+      <c r="H9" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="I9" s="21"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="23" t="s">
+      <c r="I9" s="28"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="38"/>
+      <c r="L9" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="M9" s="23" t="s">
+      <c r="M9" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="N9" s="21"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="22"/>
-      <c r="Q9" s="23" t="s">
+      <c r="N9" s="28"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="38"/>
+      <c r="Q9" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="R9" s="24" t="s">
+      <c r="R9" s="12" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="25"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="14" t="s">
+      <c r="B10" s="32"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="14"/>
-      <c r="Q10" s="14"/>
-      <c r="R10" s="15"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="24"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="25"/>
     </row>
     <row r="11" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="26">
+      <c r="B11" s="13">
         <v>1</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="13">
         <v>2</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="13">
         <v>3</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="13">
         <v>4</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="13">
         <v>5</v>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="13">
         <v>6</v>
       </c>
-      <c r="H11" s="26">
+      <c r="H11" s="13">
         <v>7</v>
       </c>
-      <c r="I11" s="26">
+      <c r="I11" s="13">
         <v>6</v>
       </c>
-      <c r="J11" s="26">
+      <c r="J11" s="13">
         <v>7</v>
       </c>
-      <c r="K11" s="26">
+      <c r="K11" s="13">
         <v>8</v>
       </c>
-      <c r="L11" s="26">
+      <c r="L11" s="13">
         <v>11</v>
       </c>
-      <c r="M11" s="26">
+      <c r="M11" s="13">
         <v>12</v>
       </c>
-      <c r="N11" s="26">
+      <c r="N11" s="13">
         <v>9</v>
       </c>
-      <c r="O11" s="26">
+      <c r="O11" s="13">
         <v>10</v>
       </c>
-      <c r="P11" s="26">
+      <c r="P11" s="13">
         <v>11</v>
       </c>
-      <c r="Q11" s="26">
+      <c r="Q11" s="13">
         <v>16</v>
       </c>
-      <c r="R11" s="26">
+      <c r="R11" s="13">
         <v>17</v>
       </c>
       <c r="S11" s="4"/>
@@ -2043,63 +1068,48 @@
         <v>15</v>
       </c>
       <c r="D12" s="3">
-        <f>'[1]2025'!E12/'[1]2025'!E15*100</f>
         <v>83.007940287182109</v>
       </c>
       <c r="E12" s="3">
-        <f>'[1]2025'!AC12/'[1]2025'!AC15*100</f>
         <v>84.674738062427551</v>
       </c>
       <c r="F12" s="3">
-        <f>'[1]2025'!K12/'[1]2025'!K15*100</f>
         <v>78.967322860741035</v>
       </c>
       <c r="G12" s="3">
-        <f>'[1]2025'!Q12/'[1]2025'!Q15*100</f>
         <v>80.622912734136776</v>
       </c>
       <c r="H12" s="3">
-        <f>'[1]2025'!W12/'[1]2025'!W15*100</f>
         <v>74.478859390363823</v>
       </c>
       <c r="I12" s="3">
-        <f>'[1]2025'!E13/'[1]2025'!E15*100</f>
         <v>79.771818368350338</v>
       </c>
       <c r="J12" s="3">
-        <f>'[1]2025'!AC13/'[1]2025'!AC15*100</f>
         <v>82.400966817595204</v>
       </c>
       <c r="K12" s="3">
-        <f>'[1]2025'!K13/'[1]2025'!K15*100</f>
         <v>73.398289918472841</v>
       </c>
       <c r="L12" s="3">
-        <f>'[1]2025'!Q13/'[1]2025'!Q15*100</f>
         <v>74.733192972266579</v>
       </c>
       <c r="M12" s="3">
-        <f>'[1]2025'!W13/'[1]2025'!W15*100</f>
         <v>69.778761061946909</v>
       </c>
       <c r="N12" s="3">
-        <f>'[1]2025'!E14/'[1]2025'!E15*100</f>
         <v>3.2361219188317594</v>
       </c>
       <c r="O12" s="3">
-        <f>'[1]2025'!AC14/'[1]2025'!AC15*100</f>
         <v>2.2732244023011132</v>
       </c>
       <c r="P12" s="3">
-        <f>'[1]2025'!K14/'[1]2025'!K15*100</f>
         <v>5.570358586862862</v>
       </c>
       <c r="Q12" s="3">
-        <f>'[1]2025'!Q14/'[1]2025'!Q15*100</f>
         <v>5.8897197618701904</v>
       </c>
       <c r="R12" s="3">
-        <f>'[1]2025'!W14/'[1]2025'!W15*100</f>
         <v>4.7000983284169129</v>
       </c>
       <c r="S12" s="4"/>
@@ -2112,63 +1122,48 @@
         <v>16</v>
       </c>
       <c r="D13" s="3">
-        <f>'[1]2025'!C12/'[1]2025'!C15*100</f>
         <v>75.426664197248698</v>
       </c>
       <c r="E13" s="3">
-        <f>'[1]2025'!AA12/'[1]2025'!AA15*100</f>
         <v>79.158900599842752</v>
       </c>
       <c r="F13" s="3">
-        <f>'[1]2025'!I12/'[1]2025'!I15*100</f>
         <v>65.984142439838649</v>
       </c>
       <c r="G13" s="3">
-        <f>'[1]2025'!O12/'[1]2025'!O15*100</f>
         <v>65.133902155032558</v>
       </c>
       <c r="H13" s="3">
-        <f>'[1]2025'!U12/'[1]2025'!U15*100</f>
         <v>68.268293933644429</v>
       </c>
       <c r="I13" s="3">
-        <f>'[1]2025'!C13/'[1]2025'!C15*100</f>
         <v>73.075725752745598</v>
       </c>
       <c r="J13" s="3">
-        <f>'[1]2025'!AA13/'[1]2025'!AA15*100</f>
         <v>77.454489473886781</v>
       </c>
       <c r="K13" s="3">
-        <f>'[1]2025'!I13/'[1]2025'!I15*100</f>
         <v>61.998887188760612</v>
       </c>
       <c r="L13" s="3">
-        <f>'[1]2025'!O13/'[1]2025'!O15*100</f>
         <v>61.100612724045135</v>
       </c>
       <c r="M13" s="3">
-        <f>'[1]2025'!U13/'[1]2025'!U15*100</f>
         <v>64.406953489564629</v>
       </c>
       <c r="N13" s="3">
-        <f>'[1]2025'!C14/'[1]2025'!C15*100</f>
         <v>2.350938444503115</v>
       </c>
       <c r="O13" s="3">
-        <f>'[1]2025'!AA14/'[1]2025'!AA15*100</f>
         <v>1.7044111259559822</v>
       </c>
       <c r="P13" s="3">
-        <f>'[1]2025'!I14/'[1]2025'!I15*100</f>
         <v>3.9866462651272778</v>
       </c>
       <c r="Q13" s="3">
-        <f>'[1]2025'!O14/'[1]2025'!O15*100</f>
         <v>4.0332894309874208</v>
       </c>
       <c r="R13" s="3">
-        <f>'[1]2025'!U14/'[1]2025'!U15*100</f>
         <v>3.8613404440797909</v>
       </c>
       <c r="S13" s="4"/>
@@ -2181,63 +1176,48 @@
         <v>7</v>
       </c>
       <c r="D14" s="3">
-        <f>'[1]2025'!G12/'[1]2025'!G15*100</f>
         <v>79.25085046301902</v>
       </c>
       <c r="E14" s="3">
-        <f>'[1]2025'!AE12/'[1]2025'!AE15*100</f>
         <v>81.924008016471603</v>
       </c>
       <c r="F14" s="3">
-        <f>'[1]2025'!M12/'[1]2025'!M15*100</f>
         <v>72.632614966909898</v>
       </c>
       <c r="G14" s="3">
-        <f>'[1]2025'!S12/'[1]2025'!S15*100</f>
         <v>73.074382471972839</v>
       </c>
       <c r="H14" s="3">
-        <f>'[1]2025'!Y12/'[1]2025'!Y15*100</f>
         <v>71.440763052208851</v>
       </c>
       <c r="I14" s="3">
-        <f>'[1]2025'!F13/'[1]2025'!G15*100</f>
         <v>79.348297316403489</v>
       </c>
       <c r="J14" s="3">
-        <f>'[1]2025'!AE13/'[1]2025'!AE15*100</f>
         <v>79.934420656396583</v>
       </c>
       <c r="K14" s="3">
-        <f>'[1]2025'!M13/'[1]2025'!M15*100</f>
         <v>67.835058544035292</v>
       </c>
       <c r="L14" s="3">
-        <f>'[1]2025'!S13/'[1]2025'!S15*100</f>
         <v>68.088570498209052</v>
       </c>
       <c r="M14" s="3">
-        <f>'[1]2025'!Y13/'[1]2025'!Y15*100</f>
         <v>67.15110441767068</v>
       </c>
       <c r="N14" s="3">
-        <f>'[1]2025'!G14/'[1]2025'!G15*100</f>
         <v>2.7974472439530227</v>
       </c>
       <c r="O14" s="3">
-        <f>'[1]2025'!AE14/'[1]2025'!AE15*100</f>
         <v>1.9895873600750105</v>
       </c>
       <c r="P14" s="3">
-        <f>'[1]2025'!M14/'[1]2025'!M15*100</f>
         <v>4.796877651450874</v>
       </c>
       <c r="Q14" s="3">
-        <f>'[1]2025'!S14/'[1]2025'!S15*100</f>
         <v>4.9848816113876353</v>
       </c>
       <c r="R14" s="3">
-        <f>'[1]2025'!Y14/'[1]2025'!Y15*100</f>
         <v>4.2896586345381529</v>
       </c>
       <c r="S14" s="4"/>
@@ -2250,63 +1230,48 @@
         <v>15</v>
       </c>
       <c r="D15" s="3">
-        <f>'[1]2024'!E12/'[1]2024'!E15*100</f>
         <v>82.400838532414127</v>
       </c>
       <c r="E15" s="3">
-        <f>'[1]2024'!AC12/'[1]2024'!AC15*100</f>
         <v>84.100114573415738</v>
       </c>
       <c r="F15" s="3">
-        <f>'[1]2024'!K12/'[1]2024'!K15*100</f>
         <v>78.108269695899125</v>
       </c>
       <c r="G15" s="3">
-        <f>'[1]2024'!Q12/'[1]2024'!Q15*100</f>
         <v>79.449667167306387</v>
       </c>
       <c r="H15" s="3">
-        <f>'[1]2024'!W12/'[1]2024'!W15*100</f>
         <v>74.429130854905139</v>
       </c>
       <c r="I15" s="3">
-        <f>'[1]2024'!E13/'[1]2024'!E15*100</f>
         <v>79.697573419755599</v>
       </c>
       <c r="J15" s="3">
-        <f>'[1]2024'!AC13/'[1]2024'!AC15*100</f>
         <v>82.063074548026705</v>
       </c>
       <c r="K15" s="3">
-        <f>'[1]2024'!K13/'[1]2024'!K15*100</f>
         <v>73.722042557817204</v>
       </c>
       <c r="L15" s="3">
-        <f>'[1]2024'!Q13/'[1]2024'!Q15*100</f>
         <v>75.125623481856465</v>
       </c>
       <c r="M15" s="3">
-        <f>'[1]2024'!W13/'[1]2024'!W15*100</f>
         <v>69.877434775975189</v>
       </c>
       <c r="N15" s="3">
-        <f>'[1]2024'!E14/'[1]2024'!E15*100</f>
         <v>2.7032651126585252</v>
       </c>
       <c r="O15" s="3">
-        <f>'[1]2024'!AC14/'[1]2024'!AC15*100</f>
         <v>2.0370400253890386</v>
       </c>
       <c r="P15" s="3">
-        <f>'[1]2024'!K14/'[1]2024'!K15*100</f>
         <v>4.3862271380819084</v>
       </c>
       <c r="Q15" s="3">
-        <f>'[1]2024'!Q14/'[1]2024'!Q15*100</f>
         <v>4.3240436854499267</v>
       </c>
       <c r="R15" s="3">
-        <f>'[1]2024'!W14/'[1]2024'!W15*100</f>
         <v>4.5567817728729088</v>
       </c>
       <c r="S15" s="4"/>
@@ -2319,63 +1284,48 @@
         <v>16</v>
       </c>
       <c r="D16" s="3">
-        <f>'[1]2024'!C12/'[1]2024'!C15*100</f>
         <v>74.995780822562992</v>
       </c>
       <c r="E16" s="3">
-        <f>'[1]2024'!AA12/'[1]2024'!AA15*100</f>
         <v>78.947196373700606</v>
       </c>
       <c r="F16" s="3">
-        <f>'[1]2024'!I12/'[1]2024'!I15*100</f>
         <v>64.813801041535086</v>
       </c>
       <c r="G16" s="3">
-        <f>'[1]2024'!O12/'[1]2024'!O15*100</f>
         <v>63.059025460093444</v>
       </c>
       <c r="H16" s="3">
-        <f>'[1]2024'!U12/'[1]2024'!U15*100</f>
         <v>69.706476656386258</v>
       </c>
       <c r="I16" s="3">
-        <f>'[1]2024'!C13/'[1]2024'!C15*100</f>
         <v>72.69152121951889</v>
       </c>
       <c r="J16" s="3">
-        <f>'[1]2024'!AA13/'[1]2024'!AA15*100</f>
         <v>77.31111207967399</v>
       </c>
       <c r="K16" s="3">
-        <f>'[1]2024'!I13/'[1]2024'!I15*100</f>
         <v>60.789433051192432</v>
       </c>
       <c r="L16" s="3">
-        <f>'[1]2024'!O13/'[1]2024'!O15*100</f>
         <v>58.985410508248307</v>
       </c>
       <c r="M16" s="3">
-        <f>'[1]2024'!U13/'[1]2024'!U15*100</f>
         <v>65.819419334255031</v>
       </c>
       <c r="N16" s="3">
-        <f>'[1]2024'!C14/'[1]2024'!C15*100</f>
         <v>2.3042596030440876</v>
       </c>
       <c r="O16" s="3">
-        <f>'[1]2024'!AA14/'[1]2024'!AA15*100</f>
         <v>1.6360842940266307</v>
       </c>
       <c r="P16" s="3">
-        <f>'[1]2024'!I14/'[1]2024'!I15*100</f>
         <v>4.0257716764222851</v>
       </c>
       <c r="Q16" s="3">
-        <f>'[1]2024'!O14/'[1]2024'!O15*100</f>
         <v>4.0736149518451414</v>
       </c>
       <c r="R16" s="3">
-        <f>'[1]2024'!U14/'[1]2024'!U15*100</f>
         <v>3.8870573221312341</v>
       </c>
       <c r="S16" s="4"/>
@@ -2388,63 +1338,48 @@
         <v>7</v>
       </c>
       <c r="D17" s="3">
-        <f>'[1]2024'!G12/'[1]2024'!G15*100</f>
         <v>78.732232786948998</v>
       </c>
       <c r="E17" s="3">
-        <f>'[1]2024'!AE12/'[1]2024'!AE15*100</f>
         <v>81.540106372900624</v>
       </c>
       <c r="F17" s="3">
-        <f>'[1]2024'!M12/'[1]2024'!M15*100</f>
         <v>71.569717264473368</v>
       </c>
       <c r="G17" s="3">
-        <f>'[1]2024'!S12/'[1]2024'!S15*100</f>
         <v>71.370550739898079</v>
       </c>
       <c r="H17" s="3">
-        <f>'[1]2024'!Y12/'[1]2024'!Y15*100</f>
         <v>72.120408640723696</v>
       </c>
       <c r="I17" s="3">
-        <f>'[1]2024'!F13/'[1]2024'!G15*100</f>
         <v>79.043535748313218</v>
       </c>
       <c r="J17" s="3">
-        <f>'[1]2024'!AE13/'[1]2024'!AE15*100</f>
         <v>79.702264145836438</v>
       </c>
       <c r="K17" s="3">
-        <f>'[1]2024'!M13/'[1]2024'!M15*100</f>
         <v>67.360789864328368</v>
       </c>
       <c r="L17" s="3">
-        <f>'[1]2024'!S13/'[1]2024'!S15*100</f>
         <v>67.169020175620034</v>
       </c>
       <c r="M17" s="3">
-        <f>'[1]2024'!Y13/'[1]2024'!Y15*100</f>
         <v>67.891029140346788</v>
       </c>
       <c r="N17" s="3">
-        <f>'[1]2024'!G14/'[1]2024'!G15*100</f>
         <v>2.5055902311925182</v>
       </c>
       <c r="O17" s="3">
-        <f>'[1]2024'!AE14/'[1]2024'!AE15*100</f>
         <v>1.8378422270641892</v>
       </c>
       <c r="P17" s="3">
-        <f>'[1]2024'!M14/'[1]2024'!M15*100</f>
         <v>4.2089274001449928</v>
       </c>
       <c r="Q17" s="3">
-        <f>'[1]2024'!S14/'[1]2024'!S15*100</f>
         <v>4.201530564278058</v>
       </c>
       <c r="R17" s="3">
-        <f>'[1]2024'!Y14/'[1]2024'!Y15*100</f>
         <v>4.2293795003769263</v>
       </c>
       <c r="S17" s="4"/>
@@ -2457,63 +1392,48 @@
         <v>15</v>
       </c>
       <c r="D18" s="3">
-        <f>'[1]2023'!E12/'[1]2023'!E15*100</f>
         <v>82.515455801424793</v>
       </c>
       <c r="E18" s="3">
-        <f>'[1]2023'!AC12/'[1]2023'!AC15*100</f>
         <v>84.103122272349651</v>
       </c>
       <c r="F18" s="3">
-        <f>'[1]2023'!K12/'[1]2023'!K15*100</f>
         <v>78.134745086663287</v>
       </c>
       <c r="G18" s="3">
-        <f>'[1]2023'!Q12/'[1]2023'!Q15*100</f>
         <v>80.127695084321445</v>
       </c>
       <c r="H18" s="3">
-        <f>'[1]2023'!W12/'[1]2023'!W15*100</f>
         <v>72.242319839219064</v>
       </c>
       <c r="I18" s="3">
-        <f>'[1]2023'!E13/'[1]2023'!E15*100</f>
         <v>79.94990853870317</v>
       </c>
       <c r="J18" s="3">
-        <f>'[1]2023'!AC13/'[1]2023'!AC15*100</f>
         <v>82.096097422469001</v>
       </c>
       <c r="K18" s="3">
-        <f>'[1]2023'!K13/'[1]2023'!K15*100</f>
         <v>74.028573500616417</v>
       </c>
       <c r="L18" s="3">
-        <f>'[1]2023'!Q13/'[1]2023'!Q15*100</f>
         <v>76.005744338139692</v>
       </c>
       <c r="M18" s="3">
-        <f>'[1]2023'!W13/'[1]2023'!W15*100</f>
         <v>68.182601205857026</v>
       </c>
       <c r="N18" s="3">
-        <f>'[1]2023'!E14/'[1]2023'!E15*100</f>
         <v>2.5655472627216103</v>
       </c>
       <c r="O18" s="3">
-        <f>'[1]2023'!AC14/'[1]2023'!AC15*100</f>
         <v>2.0070248498806409</v>
       </c>
       <c r="P18" s="3">
-        <f>'[1]2023'!K14/'[1]2023'!K15*100</f>
         <v>4.1061715860468491</v>
       </c>
       <c r="Q18" s="3">
-        <f>'[1]2023'!Q14/'[1]2023'!Q15*100</f>
         <v>4.1219507461817617</v>
       </c>
       <c r="R18" s="3">
-        <f>'[1]2023'!W14/'[1]2023'!W15*100</f>
         <v>4.0597186333620447</v>
       </c>
       <c r="S18" s="4"/>
@@ -2526,63 +1446,48 @@
         <v>16</v>
       </c>
       <c r="D19" s="3">
-        <f>'[1]2023'!C12/'[1]2023'!C15*100</f>
         <v>74.553347934918648</v>
       </c>
       <c r="E19" s="3">
-        <f>'[1]2023'!AA12/'[1]2023'!AA15*100</f>
         <v>78.588220411347365</v>
       </c>
       <c r="F19" s="3">
-        <f>'[1]2023'!I12/'[1]2023'!I15*100</f>
         <v>62.947409911617122</v>
       </c>
       <c r="G19" s="3">
-        <f>'[1]2023'!O12/'[1]2023'!O15*100</f>
         <v>62.022548547584655</v>
       </c>
       <c r="H19" s="3">
-        <f>'[1]2023'!U12/'[1]2023'!U15*100</f>
         <v>65.814458578963695</v>
       </c>
       <c r="I19" s="3">
-        <f>'[1]2023'!C13/'[1]2023'!C15*100</f>
         <v>72.661921151439287</v>
       </c>
       <c r="J19" s="3">
-        <f>'[1]2023'!AA13/'[1]2023'!AA15*100</f>
         <v>77.041714544745361</v>
       </c>
       <c r="K19" s="3">
-        <f>'[1]2023'!I13/'[1]2023'!I15*100</f>
         <v>60.063975258857241</v>
       </c>
       <c r="L19" s="3">
-        <f>'[1]2023'!O13/'[1]2023'!O15*100</f>
         <v>58.927138501043174</v>
       </c>
       <c r="M19" s="3">
-        <f>'[1]2023'!U13/'[1]2023'!U15*100</f>
         <v>63.580515048091833</v>
       </c>
       <c r="N19" s="3">
-        <f>'[1]2023'!C14/'[1]2023'!C15*100</f>
         <v>1.891426783479349</v>
       </c>
       <c r="O19" s="3">
-        <f>'[1]2023'!AA14/'[1]2023'!AA15*100</f>
         <v>1.5465058666020093</v>
       </c>
       <c r="P19" s="3">
-        <f>'[1]2023'!I14/'[1]2023'!I15*100</f>
         <v>2.8834346527598806</v>
       </c>
       <c r="Q19" s="3">
-        <f>'[1]2023'!O14/'[1]2023'!O15*100</f>
         <v>3.095410046541486</v>
       </c>
       <c r="R19" s="3">
-        <f>'[1]2023'!U14/'[1]2023'!U15*100</f>
         <v>2.2339435308718585</v>
       </c>
       <c r="S19" s="4"/>
@@ -2595,63 +1500,48 @@
         <v>7</v>
       </c>
       <c r="D20" s="3">
-        <f>'[1]2023'!G12/'[1]2023'!G15*100</f>
         <v>78.560897579092753</v>
       </c>
       <c r="E20" s="3">
-        <f>'[1]2023'!AE12/'[1]2023'!AE15*100</f>
         <v>81.349039220847587</v>
       </c>
       <c r="F20" s="3">
-        <f>'[1]2023'!M12/'[1]2023'!M15*100</f>
         <v>70.710192947734356</v>
       </c>
       <c r="G20" s="3">
-        <f>'[1]2023'!S12/'[1]2023'!S15*100</f>
         <v>71.224242185111024</v>
       </c>
       <c r="H20" s="3">
-        <f>'[1]2023'!Y12/'[1]2023'!Y15*100</f>
         <v>69.152997315836558</v>
       </c>
       <c r="I20" s="3">
-        <f>'[1]2023'!F13/'[1]2023'!G15*100</f>
         <v>78.998343068373202</v>
       </c>
       <c r="J20" s="3">
-        <f>'[1]2023'!AE13/'[1]2023'!AE15*100</f>
         <v>79.571992629639382</v>
       </c>
       <c r="K20" s="3">
-        <f>'[1]2023'!M13/'[1]2023'!M15*100</f>
         <v>67.201108912065351</v>
       </c>
       <c r="L20" s="3">
-        <f>'[1]2023'!S13/'[1]2023'!S15*100</f>
         <v>67.608037326020693</v>
       </c>
       <c r="M20" s="3">
-        <f>'[1]2023'!Y13/'[1]2023'!Y15*100</f>
         <v>65.970772442588725</v>
       </c>
       <c r="N20" s="3">
-        <f>'[1]2023'!G14/'[1]2023'!G15*100</f>
         <v>2.2307388982667291</v>
       </c>
       <c r="O20" s="3">
-        <f>'[1]2023'!AE14/'[1]2023'!AE15*100</f>
         <v>1.7767833640431694</v>
       </c>
       <c r="P20" s="3">
-        <f>'[1]2023'!M14/'[1]2023'!M15*100</f>
         <v>3.5090840356690167</v>
       </c>
       <c r="Q20" s="3">
-        <f>'[1]2023'!S14/'[1]2023'!S15*100</f>
         <v>3.6171912761277216</v>
       </c>
       <c r="R20" s="3">
-        <f>'[1]2023'!Y14/'[1]2023'!Y15*100</f>
         <v>3.1822248732478373</v>
       </c>
       <c r="S20" s="4"/>
@@ -2664,63 +1554,48 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <f>'[1]2022'!E12/'[1]2022'!E15*100</f>
         <v>82.432238912261823</v>
       </c>
       <c r="E21" s="3">
-        <f>'[1]2022'!AC12/'[1]2022'!AC15*100</f>
         <v>83.755563788542105</v>
       </c>
       <c r="F21" s="3">
-        <f>'[1]2022'!K12/'[1]2022'!K15*100</f>
         <v>78.631799790199324</v>
       </c>
       <c r="G21" s="3">
-        <f>'[1]2022'!Q12/'[1]2022'!Q15*100</f>
         <v>81.92075570716348</v>
       </c>
       <c r="H21" s="3">
-        <f>'[1]2022'!W12/'[1]2022'!W15*100</f>
         <v>69.160944955196086</v>
       </c>
       <c r="I21" s="3">
-        <f>'[1]2022'!E13/'[1]2022'!E15*100</f>
         <v>79.743856702184075</v>
       </c>
       <c r="J21" s="3">
-        <f>'[1]2022'!AC13/'[1]2022'!AC15*100</f>
         <v>81.601014396710511</v>
       </c>
       <c r="K21" s="3">
-        <f>'[1]2022'!K13/'[1]2022'!K15*100</f>
         <v>74.408811628952492</v>
       </c>
       <c r="L21" s="3">
-        <f>'[1]2022'!Q13/'[1]2022'!Q15*100</f>
         <v>77.244010253718983</v>
       </c>
       <c r="M21" s="3">
-        <f>'[1]2022'!W13/'[1]2022'!W15*100</f>
         <v>66.239962760386362</v>
       </c>
       <c r="N21" s="3">
-        <f>'[1]2022'!E14/'[1]2022'!E15*100</f>
         <v>2.6883822100777564</v>
       </c>
       <c r="O21" s="3">
-        <f>'[1]2022'!AC14/'[1]2022'!AC15*100</f>
         <v>2.1540275828241349</v>
       </c>
       <c r="P21" s="3">
-        <f>'[1]2022'!K14/'[1]2022'!K15*100</f>
         <v>4.2229881612468159</v>
       </c>
       <c r="Q21" s="3">
-        <f>'[1]2022'!Q14/'[1]2022'!Q15*100</f>
         <v>4.6767454534444832</v>
       </c>
       <c r="R21" s="3">
-        <f>'[1]2022'!W14/'[1]2022'!W15*100</f>
         <v>2.9151635051786333</v>
       </c>
       <c r="S21" s="4"/>
@@ -2733,63 +1608,48 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <f>'[1]2022'!C12/'[1]2022'!C15*100</f>
         <v>74.521449811643905</v>
       </c>
       <c r="E22" s="3">
-        <f>'[1]2022'!AA12/'[1]2022'!AA15*100</f>
         <v>77.980768728006652</v>
       </c>
       <c r="F22" s="3">
-        <f>'[1]2022'!I12/'[1]2022'!I15*100</f>
         <v>64.072962728995577</v>
       </c>
       <c r="G22" s="3">
-        <f>'[1]2022'!O12/'[1]2022'!O15*100</f>
         <v>63.841415988732628</v>
       </c>
       <c r="H22" s="3">
-        <f>'[1]2022'!U12/'[1]2022'!U15*100</f>
         <v>64.766016889961264</v>
       </c>
       <c r="I22" s="3">
-        <f>'[1]2022'!C13/'[1]2022'!C15*100</f>
         <v>72.646138012578021</v>
       </c>
       <c r="J22" s="3">
-        <f>'[1]2022'!AA13/'[1]2022'!AA15*100</f>
         <v>76.373456870813754</v>
       </c>
       <c r="K22" s="3">
-        <f>'[1]2022'!I13/'[1]2022'!I15*100</f>
         <v>61.388186986734041</v>
       </c>
       <c r="L22" s="3">
-        <f>'[1]2022'!O13/'[1]2022'!O15*100</f>
         <v>60.984633495196661</v>
       </c>
       <c r="M22" s="3">
-        <f>'[1]2022'!U13/'[1]2022'!U15*100</f>
         <v>62.600800050796877</v>
       </c>
       <c r="N22" s="3">
-        <f>'[1]2022'!C14/'[1]2022'!C15*100</f>
         <v>1.8753117990658794</v>
       </c>
       <c r="O22" s="3">
-        <f>'[1]2022'!AA14/'[1]2022'!AA15*100</f>
         <v>1.6073118571929037</v>
       </c>
       <c r="P22" s="3">
-        <f>'[1]2022'!I14/'[1]2022'!I15*100</f>
         <v>2.6847757422615288</v>
       </c>
       <c r="Q22" s="3">
-        <f>'[1]2022'!O14/'[1]2022'!O15*100</f>
         <v>2.8567824935359778</v>
       </c>
       <c r="R22" s="3">
-        <f>'[1]2022'!U14/'[1]2022'!U15*100</f>
         <v>2.1652168391643913</v>
       </c>
       <c r="S22" s="4"/>
@@ -2802,63 +1662,48 @@
         <v>7</v>
       </c>
       <c r="D23" s="3">
-        <f>'[1]2022'!G12/'[1]2022'!G15*100</f>
         <v>78.506299944827958</v>
       </c>
       <c r="E23" s="3">
-        <f>'[1]2022'!AE12/'[1]2022'!AE15*100</f>
         <v>80.871107257398947</v>
       </c>
       <c r="F23" s="3">
-        <f>'[1]2022'!M12/'[1]2022'!M15*100</f>
         <v>71.543252595155707</v>
       </c>
       <c r="G23" s="3">
-        <f>'[1]2022'!S12/'[1]2022'!S15*100</f>
         <v>73.064645674156139</v>
       </c>
       <c r="H23" s="3">
-        <f>'[1]2022'!Y12/'[1]2022'!Y15*100</f>
         <v>67.057323293660431</v>
       </c>
       <c r="I23" s="3">
-        <f>'[1]2022'!F13/'[1]2022'!G15*100</f>
         <v>78.696575239647444</v>
       </c>
       <c r="J23" s="3">
-        <f>'[1]2022'!AE13/'[1]2022'!AE15*100</f>
         <v>78.990159104917296</v>
       </c>
       <c r="K23" s="3">
-        <f>'[1]2022'!M13/'[1]2022'!M15*100</f>
         <v>68.069204152249142</v>
       </c>
       <c r="L23" s="3">
-        <f>'[1]2022'!S13/'[1]2022'!S15*100</f>
         <v>69.279403587536294</v>
       </c>
       <c r="M23" s="3">
-        <f>'[1]2022'!Y13/'[1]2022'!Y15*100</f>
         <v>64.500850133592408</v>
       </c>
       <c r="N23" s="3">
-        <f>'[1]2022'!G14/'[1]2022'!G15*100</f>
         <v>2.28486317139788</v>
       </c>
       <c r="O23" s="3">
-        <f>'[1]2022'!AE14/'[1]2022'!AE15*100</f>
         <v>1.8809481524816394</v>
       </c>
       <c r="P23" s="3">
-        <f>'[1]2022'!M14/'[1]2022'!M15*100</f>
         <v>3.4740484429065743</v>
       </c>
       <c r="Q23" s="3">
-        <f>'[1]2022'!S14/'[1]2022'!S15*100</f>
         <v>3.7852420866198484</v>
       </c>
       <c r="R23" s="3">
-        <f>'[1]2022'!Y14/'[1]2022'!Y15*100</f>
         <v>2.5564731600680108</v>
       </c>
       <c r="S23" s="4"/>
@@ -2871,63 +1716,48 @@
         <v>15</v>
       </c>
       <c r="D24" s="3">
-        <f>'[1]2021'!E12/'[1]2021'!E15*100</f>
         <v>81.201572979568354</v>
       </c>
       <c r="E24" s="3">
-        <f>'[1]2021'!AC12/'[1]2021'!AC15*100</f>
         <v>82.649277917498495</v>
       </c>
       <c r="F24" s="3">
-        <f>'[1]2021'!K12/'[1]2021'!K15*100</f>
         <v>76.874777135238219</v>
       </c>
       <c r="G24" s="3">
-        <f>'[1]2021'!Q12/'[1]2021'!Q15*100</f>
         <v>79.807426027309717</v>
       </c>
       <c r="H24" s="3">
-        <f>'[1]2021'!W12/'[1]2021'!W15*100</f>
         <v>69.034058548809654</v>
       </c>
       <c r="I24" s="3">
-        <f>'[1]2021'!E13/'[1]2021'!E15*100</f>
         <v>78.097969270942613</v>
       </c>
       <c r="J24" s="3">
-        <f>'[1]2021'!AC13/'[1]2021'!AC15*100</f>
         <v>80.179937255308658</v>
       </c>
       <c r="K24" s="3">
-        <f>'[1]2021'!K13/'[1]2021'!K15*100</f>
         <v>71.873304289855966</v>
       </c>
       <c r="L24" s="3">
-        <f>'[1]2021'!Q13/'[1]2021'!Q15*100</f>
         <v>74.567028097905975</v>
       </c>
       <c r="M24" s="3">
-        <f>'[1]2021'!W13/'[1]2021'!W15*100</f>
         <v>64.665679462353339</v>
       </c>
       <c r="N24" s="3">
-        <f>'[1]2021'!E14/'[1]2021'!E15*100</f>
         <v>3.1036037086257413</v>
       </c>
       <c r="O24" s="3">
-        <f>'[1]2021'!AC14/'[1]2021'!AC15*100</f>
         <v>2.4688221110218049</v>
       </c>
       <c r="P24" s="3">
-        <f>'[1]2021'!K14/'[1]2021'!K15*100</f>
         <v>5.0014728453822421</v>
       </c>
       <c r="Q24" s="3">
-        <f>'[1]2021'!Q14/'[1]2021'!Q15*100</f>
         <v>5.2382676863430113</v>
       </c>
       <c r="R24" s="3">
-        <f>'[1]2021'!W14/'[1]2021'!W15*100</f>
         <v>4.3683790864563159</v>
       </c>
       <c r="S24" s="4"/>
@@ -2940,63 +1770,48 @@
         <v>16</v>
       </c>
       <c r="D25" s="3">
-        <f>'[1]2021'!C12/'[1]2021'!C15*100</f>
         <v>72.885957645827787</v>
       </c>
       <c r="E25" s="3">
-        <f>'[1]2021'!AA12/'[1]2021'!AA15*100</f>
         <v>76.178741154253217</v>
       </c>
       <c r="F25" s="3">
-        <f>'[1]2021'!I12/'[1]2021'!I15*100</f>
         <v>62.228603093043169</v>
       </c>
       <c r="G25" s="3">
-        <f>'[1]2021'!O12/'[1]2021'!O15*100</f>
         <v>62.176414189837018</v>
       </c>
       <c r="H25" s="3">
-        <f>'[1]2021'!U12/'[1]2021'!U15*100</f>
         <v>62.373785482949131</v>
       </c>
       <c r="I25" s="3">
-        <f>'[1]2021'!C13/'[1]2021'!C15*100</f>
         <v>70.760718348322044</v>
       </c>
       <c r="J25" s="3">
-        <f>'[1]2021'!AA13/'[1]2021'!AA15*100</f>
         <v>74.354078900948394</v>
       </c>
       <c r="K25" s="3">
-        <f>'[1]2021'!I13/'[1]2021'!I15*100</f>
         <v>59.130522391819049</v>
       </c>
       <c r="L25" s="3">
-        <f>'[1]2021'!O13/'[1]2021'!O15*100</f>
         <v>58.91886956124732</v>
       </c>
       <c r="M25" s="3">
-        <f>'[1]2021'!U13/'[1]2021'!U15*100</f>
         <v>59.719311614910787</v>
       </c>
       <c r="N25" s="3">
-        <f>'[1]2021'!C14/'[1]2021'!C15*100</f>
         <v>2.1252392975057566</v>
       </c>
       <c r="O25" s="3">
-        <f>'[1]2021'!AA14/'[1]2021'!AA15*100</f>
         <v>1.8251810654325855</v>
       </c>
       <c r="P25" s="3">
-        <f>'[1]2021'!I14/'[1]2021'!I15*100</f>
         <v>3.0964015246922916</v>
       </c>
       <c r="Q25" s="3">
-        <f>'[1]2021'!O14/'[1]2021'!O15*100</f>
         <v>3.2575446285896912</v>
       </c>
       <c r="R25" s="3">
-        <f>'[1]2021'!U14/'[1]2021'!U15*100</f>
         <v>2.6481234520861117</v>
       </c>
       <c r="S25" s="4"/>
@@ -3009,63 +1824,48 @@
         <v>7</v>
       </c>
       <c r="D26" s="3">
-        <f>'[1]2021'!G12/'[1]2021'!G15*100</f>
         <v>77.084923486256173</v>
       </c>
       <c r="E26" s="3">
-        <f>'[1]2021'!AE12/'[1]2021'!AE15*100</f>
         <v>79.414823401877115</v>
       </c>
       <c r="F26" s="3">
-        <f>'[1]2021'!M12/'[1]2021'!M15*100</f>
         <v>69.842971609137948</v>
       </c>
       <c r="G26" s="3">
-        <f>'[1]2021'!S12/'[1]2021'!S15*100</f>
         <v>71.296653406649099</v>
       </c>
       <c r="H26" s="3">
-        <f>'[1]2021'!Y12/'[1]2021'!Y15*100</f>
         <v>65.885002251914131</v>
       </c>
       <c r="I26" s="3">
-        <f>'[1]2021'!F13/'[1]2021'!G15*100</f>
         <v>76.5557336744845</v>
       </c>
       <c r="J26" s="3">
-        <f>'[1]2021'!AE13/'[1]2021'!AE15*100</f>
         <v>77.267740856291482</v>
       </c>
       <c r="K26" s="3">
-        <f>'[1]2021'!M13/'[1]2021'!M15*100</f>
         <v>65.756041723765463</v>
       </c>
       <c r="L26" s="3">
-        <f>'[1]2021'!S13/'[1]2021'!S15*100</f>
         <v>67.013410616094944</v>
       </c>
       <c r="M26" s="3">
-        <f>'[1]2021'!Y13/'[1]2021'!Y15*100</f>
         <v>62.329980483410893</v>
       </c>
       <c r="N26" s="3">
-        <f>'[1]2021'!G14/'[1]2021'!G15*100</f>
         <v>2.6192639218910343</v>
       </c>
       <c r="O26" s="3">
-        <f>'[1]2021'!AE14/'[1]2021'!AE15*100</f>
         <v>2.1470825455856306</v>
       </c>
       <c r="P26" s="3">
-        <f>'[1]2021'!M14/'[1]2021'!M15*100</f>
         <v>4.0869298853724993</v>
       </c>
       <c r="Q26" s="3">
-        <f>'[1]2021'!S14/'[1]2021'!S15*100</f>
         <v>4.2821408500369147</v>
       </c>
       <c r="R26" s="3">
-        <f>'[1]2021'!Y14/'[1]2021'!Y15*100</f>
         <v>3.5550217685032277</v>
       </c>
       <c r="S26" s="4"/>
@@ -4692,197 +3492,185 @@
     </row>
     <row r="57" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="2"/>
-      <c r="C57" s="27"/>
-      <c r="D57" s="27"/>
-      <c r="E57" s="27"/>
-      <c r="F57" s="27"/>
-      <c r="G57" s="27"/>
-      <c r="H57" s="27"/>
-      <c r="I57" s="27"/>
-      <c r="J57" s="27"/>
-      <c r="K57" s="27"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="14"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="14"/>
+      <c r="G57" s="14"/>
+      <c r="H57" s="14"/>
+      <c r="I57" s="14"/>
+      <c r="J57" s="14"/>
+      <c r="K57" s="14"/>
     </row>
     <row r="58" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B58" s="28"/>
-      <c r="C58" s="29"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
-      <c r="F58" s="29"/>
-      <c r="G58" s="29"/>
-      <c r="H58" s="29"/>
-      <c r="I58" s="29"/>
-      <c r="J58" s="29"/>
-      <c r="K58" s="29"/>
-      <c r="N58" s="30"/>
-    </row>
-    <row r="59" spans="2:19" s="32" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="31" t="s">
+      <c r="B58" s="15"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="16"/>
+      <c r="E58" s="16"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="16"/>
+      <c r="H58" s="16"/>
+      <c r="I58" s="16"/>
+      <c r="J58" s="16"/>
+      <c r="K58" s="16"/>
+      <c r="N58" s="17"/>
+    </row>
+    <row r="59" spans="2:19" s="18" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="C59" s="31"/>
-      <c r="D59" s="31"/>
-      <c r="E59" s="31"/>
-      <c r="F59" s="31"/>
-      <c r="G59" s="31"/>
-      <c r="H59" s="31"/>
-      <c r="I59" s="31"/>
-      <c r="J59" s="31"/>
-      <c r="K59" s="31"/>
+      <c r="C59" s="33"/>
+      <c r="D59" s="33"/>
+      <c r="E59" s="33"/>
+      <c r="F59" s="33"/>
+      <c r="G59" s="33"/>
+      <c r="H59" s="33"/>
+      <c r="I59" s="33"/>
+      <c r="J59" s="33"/>
+      <c r="K59" s="33"/>
     </row>
     <row r="60" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B60" s="29" t="s">
+      <c r="B60" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C60" s="29"/>
-      <c r="D60" s="29"/>
-      <c r="E60" s="29"/>
-      <c r="F60" s="29"/>
-      <c r="G60" s="29"/>
-      <c r="H60" s="29"/>
-      <c r="I60" s="29"/>
-      <c r="J60" s="29"/>
-      <c r="K60" s="29"/>
-      <c r="N60" s="30"/>
+      <c r="C60" s="16"/>
+      <c r="D60" s="16"/>
+      <c r="E60" s="16"/>
+      <c r="F60" s="16"/>
+      <c r="G60" s="16"/>
+      <c r="H60" s="16"/>
+      <c r="I60" s="16"/>
+      <c r="J60" s="16"/>
+      <c r="K60" s="16"/>
+      <c r="N60" s="17"/>
     </row>
     <row r="61" spans="2:19" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="33" t="s">
+      <c r="B61" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="C61" s="33"/>
-      <c r="D61" s="33"/>
-      <c r="E61" s="33"/>
-      <c r="F61" s="33"/>
-      <c r="G61" s="33"/>
-      <c r="H61" s="33"/>
-      <c r="I61" s="33"/>
-      <c r="J61" s="33"/>
-      <c r="K61" s="33"/>
+      <c r="C61" s="34"/>
+      <c r="D61" s="34"/>
+      <c r="E61" s="34"/>
+      <c r="F61" s="34"/>
+      <c r="G61" s="34"/>
+      <c r="H61" s="34"/>
+      <c r="I61" s="34"/>
+      <c r="J61" s="34"/>
+      <c r="K61" s="34"/>
     </row>
     <row r="62" spans="2:19" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="33" t="s">
+      <c r="B62" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="C62" s="33"/>
-      <c r="D62" s="33"/>
-      <c r="E62" s="33"/>
-      <c r="F62" s="33"/>
-      <c r="G62" s="33"/>
-      <c r="H62" s="33"/>
-      <c r="I62" s="33"/>
-      <c r="J62" s="33"/>
-      <c r="K62" s="33"/>
+      <c r="C62" s="34"/>
+      <c r="D62" s="34"/>
+      <c r="E62" s="34"/>
+      <c r="F62" s="34"/>
+      <c r="G62" s="34"/>
+      <c r="H62" s="34"/>
+      <c r="I62" s="34"/>
+      <c r="J62" s="34"/>
+      <c r="K62" s="34"/>
     </row>
     <row r="63" spans="2:19" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="34" t="s">
+      <c r="B63" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C63" s="35"/>
-      <c r="D63" s="35"/>
-      <c r="E63" s="35"/>
-      <c r="F63" s="35"/>
-      <c r="G63" s="35"/>
-      <c r="H63" s="35"/>
-      <c r="I63" s="35"/>
-      <c r="J63" s="35"/>
-      <c r="K63" s="35"/>
+      <c r="C63" s="20"/>
+      <c r="D63" s="20"/>
+      <c r="E63" s="20"/>
+      <c r="F63" s="20"/>
+      <c r="G63" s="20"/>
+      <c r="H63" s="20"/>
+      <c r="I63" s="20"/>
+      <c r="J63" s="20"/>
+      <c r="K63" s="20"/>
     </row>
     <row r="64" spans="2:19" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="35"/>
-      <c r="C64" s="35"/>
-      <c r="D64" s="35"/>
-      <c r="E64" s="35"/>
-      <c r="F64" s="35"/>
-      <c r="G64" s="35"/>
-      <c r="H64" s="35"/>
-      <c r="I64" s="35"/>
-      <c r="J64" s="35"/>
-      <c r="K64" s="35"/>
-    </row>
-    <row r="65" spans="2:11" s="32" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="36" t="s">
+      <c r="B64" s="20"/>
+      <c r="C64" s="20"/>
+      <c r="D64" s="20"/>
+      <c r="E64" s="20"/>
+      <c r="F64" s="20"/>
+      <c r="G64" s="20"/>
+      <c r="H64" s="20"/>
+      <c r="I64" s="20"/>
+      <c r="J64" s="20"/>
+      <c r="K64" s="20"/>
+    </row>
+    <row r="65" spans="2:11" s="18" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C65" s="37"/>
-      <c r="D65" s="37"/>
-      <c r="E65" s="37"/>
-      <c r="F65" s="37"/>
-      <c r="G65" s="37"/>
-      <c r="H65" s="37"/>
-      <c r="I65" s="37"/>
-      <c r="J65" s="37"/>
-      <c r="K65" s="37"/>
+      <c r="C65" s="22"/>
+      <c r="D65" s="22"/>
+      <c r="E65" s="22"/>
+      <c r="F65" s="22"/>
+      <c r="G65" s="22"/>
+      <c r="H65" s="22"/>
+      <c r="I65" s="22"/>
+      <c r="J65" s="22"/>
+      <c r="K65" s="22"/>
     </row>
     <row r="66" spans="2:11" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="2:11" s="32" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="36" t="s">
+    <row r="67" spans="2:11" s="18" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C67" s="37"/>
-      <c r="D67" s="37"/>
-      <c r="E67" s="37"/>
-      <c r="F67" s="37"/>
-      <c r="G67" s="37"/>
-      <c r="H67" s="37"/>
-      <c r="I67" s="37"/>
-      <c r="J67" s="37"/>
-      <c r="K67" s="37"/>
-    </row>
-    <row r="68" spans="2:11" s="32" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="36" t="s">
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="22"/>
+      <c r="K67" s="22"/>
+    </row>
+    <row r="68" spans="2:11" s="18" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C68" s="37"/>
-      <c r="D68" s="37"/>
-      <c r="E68" s="37"/>
-      <c r="F68" s="37"/>
-      <c r="G68" s="37"/>
-      <c r="H68" s="37"/>
-      <c r="I68" s="37"/>
-      <c r="J68" s="37"/>
-      <c r="K68" s="37"/>
-    </row>
-    <row r="69" spans="2:11" s="32" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="36" t="s">
+      <c r="C68" s="22"/>
+      <c r="D68" s="22"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="22"/>
+      <c r="G68" s="22"/>
+      <c r="H68" s="22"/>
+      <c r="I68" s="22"/>
+      <c r="J68" s="22"/>
+      <c r="K68" s="22"/>
+    </row>
+    <row r="69" spans="2:11" s="18" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C69" s="37"/>
-      <c r="D69" s="37"/>
-      <c r="E69" s="37"/>
-      <c r="F69" s="37"/>
-      <c r="G69" s="37"/>
-      <c r="H69" s="37"/>
-      <c r="I69" s="37"/>
-      <c r="J69" s="37"/>
-      <c r="K69" s="37"/>
-    </row>
-    <row r="70" spans="2:11" s="32" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="38" t="s">
+      <c r="C69" s="22"/>
+      <c r="D69" s="22"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="22"/>
+      <c r="G69" s="22"/>
+      <c r="H69" s="22"/>
+      <c r="I69" s="22"/>
+      <c r="J69" s="22"/>
+      <c r="K69" s="22"/>
+    </row>
+    <row r="70" spans="2:11" s="18" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="C70" s="37"/>
-      <c r="D70" s="37"/>
-      <c r="E70" s="37"/>
-      <c r="F70" s="37"/>
-      <c r="G70" s="37"/>
-      <c r="H70" s="37"/>
-      <c r="I70" s="37"/>
-      <c r="J70" s="37"/>
-      <c r="K70" s="37"/>
+      <c r="C70" s="22"/>
+      <c r="D70" s="22"/>
+      <c r="E70" s="22"/>
+      <c r="F70" s="22"/>
+      <c r="G70" s="22"/>
+      <c r="H70" s="22"/>
+      <c r="I70" s="22"/>
+      <c r="J70" s="22"/>
+      <c r="K70" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="N6:R6"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="J7:M7"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B6:B10"/>
-    <mergeCell ref="C6:C10"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="I6:M6"/>
-    <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="D10:R10"/>
     <mergeCell ref="B59:K59"/>
     <mergeCell ref="B61:K61"/>
     <mergeCell ref="B62:K62"/>
@@ -4896,6 +3684,18 @@
     <mergeCell ref="L8:M8"/>
     <mergeCell ref="O8:O9"/>
     <mergeCell ref="P8:P9"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B6:B10"/>
+    <mergeCell ref="C6:C10"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="I6:M6"/>
+    <mergeCell ref="D10:R10"/>
+    <mergeCell ref="N6:R6"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="J7:M7"/>
+    <mergeCell ref="Q8:R8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B70" r:id="rId1" xr:uid="{3ECA3C8E-D001-4E48-A48D-3E856F57D422}"/>

--- a/assets/excel/2026_5-1-2.xlsx
+++ b/assets/excel/2026_5-1-2.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Hannover\Dez15_Uebergreifende_Analysen\Projekte\Integrationsmonitoring\Schlesier\MT_Site\assets\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BiesterChristophLSN\Desktop\MZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDDAC2CE-14AE-452E-A80B-3956D7DA8F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{784EAAA1-CD3C-44F2-B823-7F0E24E73403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{4424B46B-A95E-48DA-B113-8E8F86BF46C8}"/>
+    <workbookView xWindow="20052" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4424B46B-A95E-48DA-B113-8E8F86BF46C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -140,9 +140,6 @@
     <t xml:space="preserve">Frauen </t>
   </si>
   <si>
-    <t xml:space="preserve">1) Hochrechnung anhand der Bevölkerungsfortschreibung auf Basis des Zensus 2011. Die Hochrechnung für die Jahre vor 2011 sowie für bislang veröffentlichte Ergebnisse des Mikrozensus 2011-2013 basiert auf den fortgeschriebenen Ergebnissen der Volkszählung 1987. In 2016 erfolgte die Umstellung auf eine neue Mikrozensus-Stichprobe. Ab 2017 wird nur noch die Bevölkerung in Privathaushalten (ohne Gemeinschaftsunterkünfte) ausgewiesen. Dadurch ergibt sich jeweils eine eingeschränkte Vergleichbarkeit mit den Vorjahren. </t>
-  </si>
-  <si>
     <t>2) Bezogen auf die Bevölkerung im Erwerbsalter (15 bis unter 65 Jahre).</t>
   </si>
   <si>
@@ -171,6 +168,9 @@
   </si>
   <si>
     <t>© Landesamt für Statistik Niedersachsen, Hannover 2026,                                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1)  Ab der Veröffentlichung der Endergebnisse 2023 und der Erstergebnisse 2024 werden für die Hochrechnung des Mikrozensus Daten der Bevölkerungsfortschreibung herangezogen, die auf den Eckwerten des Zensus 2022 basieren. Die Hochrechnung für die Jahre vor 2011 sowie für bislang veröffentlichte Ergebnisse des Mikrozensus 2011-2013 basiert auf den fortgeschriebenen Ergebnissen der Volkszählung 1987. In 2016 erfolgte die Umstellung auf eine neue Mikrozensus-Stichprobe (auf Basis des Zensus 2011). Ab 2017 wird nur noch die Bevölkerung in Privathaushalten (ohne Gemeinschaftsunterkünfte) ausgewiesen. Dadurch ergibt sich jeweils eine eingeschränkte Vergleichbarkeit mit den Vorjahren. </t>
   </si>
 </sst>
 </file>
@@ -442,11 +442,11 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -455,6 +455,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
@@ -470,22 +485,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -508,9 +508,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -548,7 +548,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -654,7 +654,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -796,7 +796,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -823,22 +823,22 @@
   <sheetData>
     <row r="1" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
       <c r="M3" s="8"/>
     </row>
     <row r="4" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -858,36 +858,36 @@
       <c r="I5" s="10"/>
     </row>
     <row r="6" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="35" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24" t="s">
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="24"/>
-      <c r="N6" s="24" t="s">
+      <c r="J6" s="33"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="33"/>
+      <c r="M6" s="33"/>
+      <c r="N6" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="O6" s="24"/>
-      <c r="P6" s="24"/>
-      <c r="Q6" s="24"/>
-      <c r="R6" s="25"/>
+      <c r="O6" s="33"/>
+      <c r="P6" s="33"/>
+      <c r="Q6" s="33"/>
+      <c r="R6" s="38"/>
     </row>
     <row r="7" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="31"/>
+      <c r="B7" s="36"/>
       <c r="C7" s="27"/>
       <c r="D7" s="26" t="s">
         <v>7</v>
@@ -915,51 +915,51 @@
       </c>
       <c r="P7" s="26"/>
       <c r="Q7" s="26"/>
-      <c r="R7" s="35"/>
+      <c r="R7" s="29"/>
     </row>
     <row r="8" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="31"/>
+      <c r="B8" s="36"/>
       <c r="C8" s="27"/>
       <c r="D8" s="27"/>
-      <c r="E8" s="36" t="s">
+      <c r="E8" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="37" t="s">
+      <c r="F8" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="G8" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="24"/>
+      <c r="H8" s="33"/>
       <c r="I8" s="27"/>
-      <c r="J8" s="36" t="s">
+      <c r="J8" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="K8" s="37" t="s">
+      <c r="K8" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="24" t="s">
+      <c r="L8" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="M8" s="24"/>
+      <c r="M8" s="33"/>
       <c r="N8" s="27"/>
-      <c r="O8" s="36" t="s">
+      <c r="O8" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="P8" s="37" t="s">
+      <c r="P8" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="Q8" s="24" t="s">
+      <c r="Q8" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="R8" s="25"/>
+      <c r="R8" s="38"/>
     </row>
     <row r="9" spans="2:19" s="5" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="31"/>
+      <c r="B9" s="36"/>
       <c r="C9" s="27"/>
       <c r="D9" s="28"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="38"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="32"/>
       <c r="G9" s="11" t="s">
         <v>12</v>
       </c>
@@ -967,8 +967,8 @@
         <v>13</v>
       </c>
       <c r="I9" s="28"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="38"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="32"/>
       <c r="L9" s="11" t="s">
         <v>12</v>
       </c>
@@ -976,8 +976,8 @@
         <v>13</v>
       </c>
       <c r="N9" s="28"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="38"/>
+      <c r="O9" s="30"/>
+      <c r="P9" s="32"/>
       <c r="Q9" s="11" t="s">
         <v>12</v>
       </c>
@@ -986,25 +986,25 @@
       </c>
     </row>
     <row r="10" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="32"/>
+      <c r="B10" s="37"/>
       <c r="C10" s="28"/>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="24"/>
-      <c r="N10" s="24"/>
-      <c r="O10" s="24"/>
-      <c r="P10" s="24"/>
-      <c r="Q10" s="24"/>
-      <c r="R10" s="25"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="33"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="33"/>
+      <c r="O10" s="33"/>
+      <c r="P10" s="33"/>
+      <c r="Q10" s="33"/>
+      <c r="R10" s="38"/>
     </row>
     <row r="11" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="13">
@@ -3516,22 +3516,22 @@
       <c r="N58" s="17"/>
     </row>
     <row r="59" spans="2:19" s="18" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="C59" s="33"/>
-      <c r="D59" s="33"/>
-      <c r="E59" s="33"/>
-      <c r="F59" s="33"/>
-      <c r="G59" s="33"/>
-      <c r="H59" s="33"/>
-      <c r="I59" s="33"/>
-      <c r="J59" s="33"/>
-      <c r="K59" s="33"/>
+      <c r="B59" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C59" s="24"/>
+      <c r="D59" s="24"/>
+      <c r="E59" s="24"/>
+      <c r="F59" s="24"/>
+      <c r="G59" s="24"/>
+      <c r="H59" s="24"/>
+      <c r="I59" s="24"/>
+      <c r="J59" s="24"/>
+      <c r="K59" s="24"/>
     </row>
     <row r="60" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B60" s="16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C60" s="16"/>
       <c r="D60" s="16"/>
@@ -3545,36 +3545,36 @@
       <c r="N60" s="17"/>
     </row>
     <row r="61" spans="2:19" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="34" t="s">
+      <c r="B61" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="25"/>
+      <c r="D61" s="25"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="25"/>
+      <c r="G61" s="25"/>
+      <c r="H61" s="25"/>
+      <c r="I61" s="25"/>
+      <c r="J61" s="25"/>
+      <c r="K61" s="25"/>
+    </row>
+    <row r="62" spans="2:19" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="C61" s="34"/>
-      <c r="D61" s="34"/>
-      <c r="E61" s="34"/>
-      <c r="F61" s="34"/>
-      <c r="G61" s="34"/>
-      <c r="H61" s="34"/>
-      <c r="I61" s="34"/>
-      <c r="J61" s="34"/>
-      <c r="K61" s="34"/>
-    </row>
-    <row r="62" spans="2:19" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="C62" s="34"/>
-      <c r="D62" s="34"/>
-      <c r="E62" s="34"/>
-      <c r="F62" s="34"/>
-      <c r="G62" s="34"/>
-      <c r="H62" s="34"/>
-      <c r="I62" s="34"/>
-      <c r="J62" s="34"/>
-      <c r="K62" s="34"/>
+      <c r="C62" s="25"/>
+      <c r="D62" s="25"/>
+      <c r="E62" s="25"/>
+      <c r="F62" s="25"/>
+      <c r="G62" s="25"/>
+      <c r="H62" s="25"/>
+      <c r="I62" s="25"/>
+      <c r="J62" s="25"/>
+      <c r="K62" s="25"/>
     </row>
     <row r="63" spans="2:19" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C63" s="20"/>
       <c r="D63" s="20"/>
@@ -3600,7 +3600,7 @@
     </row>
     <row r="65" spans="2:11" s="18" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C65" s="22"/>
       <c r="D65" s="22"/>
@@ -3615,7 +3615,7 @@
     <row r="66" spans="2:11" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="67" spans="2:11" s="18" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C67" s="22"/>
       <c r="D67" s="22"/>
@@ -3629,7 +3629,7 @@
     </row>
     <row r="68" spans="2:11" s="18" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C68" s="22"/>
       <c r="D68" s="22"/>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="69" spans="2:11" s="18" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C69" s="22"/>
       <c r="D69" s="22"/>
@@ -3657,7 +3657,7 @@
     </row>
     <row r="70" spans="2:11" s="18" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C70" s="22"/>
       <c r="D70" s="22"/>
@@ -3671,6 +3671,18 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B6:B10"/>
+    <mergeCell ref="C6:C10"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="I6:M6"/>
+    <mergeCell ref="D10:R10"/>
+    <mergeCell ref="N6:R6"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="J7:M7"/>
+    <mergeCell ref="Q8:R8"/>
     <mergeCell ref="B59:K59"/>
     <mergeCell ref="B61:K61"/>
     <mergeCell ref="B62:K62"/>
@@ -3684,18 +3696,6 @@
     <mergeCell ref="L8:M8"/>
     <mergeCell ref="O8:O9"/>
     <mergeCell ref="P8:P9"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B6:B10"/>
-    <mergeCell ref="C6:C10"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="I6:M6"/>
-    <mergeCell ref="D10:R10"/>
-    <mergeCell ref="N6:R6"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="J7:M7"/>
-    <mergeCell ref="Q8:R8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B70" r:id="rId1" xr:uid="{3ECA3C8E-D001-4E48-A48D-3E856F57D422}"/>
